--- a/discrete_pinn/output_dir/dataset_splits.xlsx
+++ b/discrete_pinn/output_dir/dataset_splits.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -423,7 +423,7 @@
           <t>Train</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
@@ -438,35 +438,67 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>y_n</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>x_n+1</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>y_n+1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>x_n</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>y_n</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>x_n+1</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>y_n+1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.04224605858325958</v>
+        <v>0.9049077033996582</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1614407002925873</v>
+        <v>-0.159072682261467</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9580821990966797</v>
+        <v>-0.305473804473877</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1602412760257721</v>
+        <v>0.271472305059433</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.06086546182632446</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.2889116406440735</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.7059019207954407</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.01825963892042637</v>
       </c>
     </row>
     <row r="5">
@@ -474,16 +506,28 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1614407002925873</v>
+        <v>-0.305473804473877</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5401566028594971</v>
+        <v>0.271472305059433</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1602412760257721</v>
+        <v>1.140832304954529</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5369104146957397</v>
+        <v>-0.09164214134216309</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.7059019207954407</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.01825963892042637</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.3206431567668915</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.2117705643177032</v>
       </c>
     </row>
     <row r="6">
@@ -491,16 +535,28 @@
         <v>2</v>
       </c>
       <c r="B6" t="n">
-        <v>0.5401566028594971</v>
+        <v>1.140832304954529</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9910659193992615</v>
+        <v>-0.09164214134216309</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5369104146957397</v>
+        <v>-0.9137399792671204</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9920641183853149</v>
+        <v>0.342249721288681</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.3206431567668915</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.2117705643177032</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.067833781242371</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.09619294106960297</v>
       </c>
     </row>
     <row r="7">
@@ -508,16 +564,28 @@
         <v>3</v>
       </c>
       <c r="B7" t="n">
-        <v>0.9910659193992615</v>
+        <v>-0.9137399792671204</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03532855957746506</v>
+        <v>0.342249721288681</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9920641183853149</v>
+        <v>0.173360601067543</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03141291439533234</v>
+        <v>-0.2741219997406006</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.067833781242371</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.09619294106960297</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.5001834630966187</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.3203501105308533</v>
       </c>
     </row>
     <row r="8">
@@ -525,16 +593,28 @@
         <v>4</v>
       </c>
       <c r="B8" t="n">
-        <v>0.03532855957746506</v>
+        <v>0.173360601067543</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1359809935092926</v>
+        <v>-0.2741219997406006</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03141291439533234</v>
+        <v>0.6838025450706482</v>
       </c>
       <c r="E8" t="n">
-        <v>0.121400311589241</v>
+        <v>0.05200818181037903</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.5001834630966187</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.3203501105308533</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.9700931906700134</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-0.1500550508499146</v>
       </c>
     </row>
     <row r="9">
@@ -542,16 +622,28 @@
         <v>5</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1359809935092926</v>
+        <v>0.6838025450706482</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4687857627868652</v>
+        <v>0.05200818181037903</v>
       </c>
       <c r="D9" t="n">
-        <v>0.121400311589241</v>
+        <v>0.3973878920078278</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4255824983119965</v>
+        <v>0.2051407694816589</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9700931906700134</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.1500550508499146</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.4675681889057159</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.2910279631614685</v>
       </c>
     </row>
     <row r="10">
@@ -559,16 +651,28 @@
         <v>6</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4687857627868652</v>
+        <v>0.3973878920078278</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9936124086380005</v>
+        <v>0.2051407694816589</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4255824983119965</v>
+        <v>0.9840567708015442</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9754034876823425</v>
+        <v>0.1192163676023483</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.4675681889057159</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.2910279631614685</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.9849599599838257</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.1402704566717148</v>
       </c>
     </row>
     <row r="11">
@@ -576,16 +680,28 @@
         <v>7</v>
       </c>
       <c r="B11" t="n">
-        <v>0.9936124086380005</v>
+        <v>0.9840567708015442</v>
       </c>
       <c r="C11" t="n">
-        <v>0.02532360889017582</v>
+        <v>0.1192163676023483</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9754034876823425</v>
+        <v>-0.2364984154701233</v>
       </c>
       <c r="E11" t="n">
-        <v>0.09572606533765793</v>
+        <v>0.2952170372009277</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9849599599838257</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.1402704566717148</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.4984749853610992</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.2954879701137543</v>
       </c>
     </row>
     <row r="12">
@@ -593,16 +709,28 @@
         <v>8</v>
       </c>
       <c r="B12" t="n">
-        <v>0.02532360889017582</v>
+        <v>-0.2364984154701233</v>
       </c>
       <c r="C12" t="n">
-        <v>0.09848247468471527</v>
+        <v>0.2952170372009277</v>
       </c>
       <c r="D12" t="n">
-        <v>0.09572606533765793</v>
+        <v>1.216912865638733</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3453847169876099</v>
+        <v>-0.07094952464103699</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.4984749853610992</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.2954879701137543</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.9476197361946106</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0.1495424956083298</v>
       </c>
     </row>
     <row r="13">
@@ -610,16 +738,28 @@
         <v>9</v>
       </c>
       <c r="B13" t="n">
-        <v>0.09848247468471527</v>
+        <v>1.216912865638733</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3542468547821045</v>
+        <v>-0.07094952464103699</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3453847169876099</v>
+        <v>-1.144177436828613</v>
       </c>
       <c r="E13" t="n">
-        <v>0.902115523815155</v>
+        <v>0.3650738894939423</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.9476197361946106</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.1495424956083298</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.406718909740448</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.2842859327793121</v>
       </c>
     </row>
     <row r="14">
@@ -627,16 +767,28 @@
         <v>10</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3542468547821045</v>
+        <v>-1.144177436828613</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9127365350723267</v>
+        <v>0.3650738894939423</v>
       </c>
       <c r="D14" t="n">
-        <v>0.902115523815155</v>
+        <v>-0.4677248597145081</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3523293733596802</v>
+        <v>-0.3432532250881195</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.406718909740448</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.2842859327793121</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.052697539329529</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-0.1220156773924828</v>
       </c>
     </row>
     <row r="15">
@@ -644,16 +796,28 @@
         <v>11</v>
       </c>
       <c r="B15" t="n">
-        <v>0.9127365350723267</v>
+        <v>-0.4677248597145081</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3177977502346039</v>
+        <v>-0.3432532250881195</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3523293733596802</v>
+        <v>0.3504735827445984</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9104915857315063</v>
+        <v>-0.1403174549341202</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.052697539329529</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.1220156773924828</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.673456609249115</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.3158092498779297</v>
       </c>
     </row>
     <row r="16">
@@ -661,16 +825,28 @@
         <v>12</v>
       </c>
       <c r="B16" t="n">
-        <v>0.3177977502346039</v>
+        <v>0.3504735827445984</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8650413155555725</v>
+        <v>-0.1403174549341202</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9104915857315063</v>
+        <v>0.6877180933952332</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3251715898513794</v>
+        <v>0.1051420792937279</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-0.673456609249115</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.3158092498779297</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.6808479428291321</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-0.20203697681427</v>
       </c>
     </row>
     <row r="17">
@@ -678,16 +854,28 @@
         <v>13</v>
       </c>
       <c r="B17" t="n">
-        <v>0.8650413155555725</v>
+        <v>0.6877180933952332</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4658118784427643</v>
+        <v>0.1051420792937279</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3251715898513794</v>
+        <v>0.4430034160614014</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8755457401275635</v>
+        <v>0.2063154280185699</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.6808479428291321</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.20203697681427</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.1489874869585037</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.2042543888092041</v>
       </c>
     </row>
     <row r="18">
@@ -695,16 +883,28 @@
         <v>14</v>
       </c>
       <c r="B18" t="n">
-        <v>0.4658118784427643</v>
+        <v>0.4430034160614014</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9928363561630249</v>
+        <v>0.2063154280185699</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8755457401275635</v>
+        <v>0.931562602519989</v>
       </c>
       <c r="E18" t="n">
-        <v>0.434771865606308</v>
+        <v>0.1329010277986526</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.1489874869585037</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.2042543888092041</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.173178195953369</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.04469624906778336</v>
       </c>
     </row>
     <row r="19">
@@ -712,16 +912,28 @@
         <v>15</v>
       </c>
       <c r="B19" t="n">
-        <v>0.9928363561630249</v>
+        <v>0.931562602519989</v>
       </c>
       <c r="C19" t="n">
-        <v>0.028378089889884</v>
+        <v>0.1329010277986526</v>
       </c>
       <c r="D19" t="n">
-        <v>0.434771865606308</v>
+        <v>-0.08203138411045074</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9805237054824829</v>
+        <v>0.2794687747955322</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.173178195953369</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.04469624906778336</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.8821896910667419</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.3519534766674042</v>
       </c>
     </row>
     <row r="20">
@@ -729,16 +941,28 @@
         <v>16</v>
       </c>
       <c r="B20" t="n">
-        <v>0.028378089889884</v>
+        <v>-0.08203138411045074</v>
       </c>
       <c r="C20" t="n">
-        <v>0.110015369951725</v>
+        <v>0.2794687747955322</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9805237054824829</v>
+        <v>1.270048022270203</v>
       </c>
       <c r="E20" t="n">
-        <v>0.07619690895080566</v>
+        <v>-0.02460941672325134</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-0.8821896910667419</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.3519534766674042</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.2623913288116455</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-0.2646569013595581</v>
       </c>
     </row>
     <row r="21">
@@ -746,16 +970,28 @@
         <v>17</v>
       </c>
       <c r="B21" t="n">
-        <v>0.110015369951725</v>
+        <v>1.270048022270203</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3906688392162323</v>
+        <v>-0.02460941672325134</v>
       </c>
       <c r="D21" t="n">
-        <v>0.07619690895080566</v>
+        <v>-1.282840013504028</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2808598577976227</v>
+        <v>0.3810143768787384</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.2623913288116455</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-0.2646569013595581</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.638954222202301</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.07871739566326141</v>
       </c>
     </row>
     <row r="22">
@@ -763,16 +999,28 @@
         <v>18</v>
       </c>
       <c r="B22" t="n">
-        <v>0.3906688392162323</v>
+        <v>-1.282840013504028</v>
       </c>
       <c r="C22" t="n">
-        <v>0.9498063325881958</v>
+        <v>0.3810143768787384</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2808598577976227</v>
+        <v>-0.9229354858398438</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8058906197547913</v>
+        <v>-0.3848519921302795</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.638954222202301</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.07871739566326141</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.5071499347686768</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.1916862577199936</v>
       </c>
     </row>
     <row r="23">
@@ -780,16 +1028,28 @@
         <v>19</v>
       </c>
       <c r="B23" t="n">
-        <v>0.9498063325881958</v>
+        <v>-0.9229354858398438</v>
       </c>
       <c r="C23" t="n">
-        <v>0.19022037088871</v>
+        <v>-0.3848519921302795</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8058906197547913</v>
+        <v>-0.5773858428001404</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6241594552993774</v>
+        <v>-0.2768806517124176</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.5071499347686768</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.1916862577199936</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.8316047787666321</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.1521449834108353</v>
       </c>
     </row>
     <row r="24">
@@ -797,16 +1057,28 @@
         <v>20</v>
       </c>
       <c r="B24" t="n">
-        <v>0.19022037088871</v>
+        <v>-0.5773858428001404</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6146059632301331</v>
+        <v>-0.2768806517124176</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6241594552993774</v>
+        <v>0.2563952207565308</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9359918832778931</v>
+        <v>-0.1732157468795776</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.8316047787666321</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.1521449834108353</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1839518845081329</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.2494814246892929</v>
       </c>
     </row>
     <row r="25">
@@ -814,16 +1086,28 @@
         <v>21</v>
       </c>
       <c r="B25" t="n">
-        <v>0.6146059632301331</v>
+        <v>0.2563952207565308</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9450932145118713</v>
+        <v>-0.1732157468795776</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9359918832778931</v>
+        <v>0.7347503304481506</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2390451282262802</v>
+        <v>0.07691856473684311</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.1839518845081329</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.2494814246892929</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.202107787132263</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.05518556758761406</v>
       </c>
     </row>
     <row r="26">
@@ -831,16 +1115,28 @@
         <v>22</v>
       </c>
       <c r="B26" t="n">
-        <v>0.9450932145118713</v>
+        <v>0.7347503304481506</v>
       </c>
       <c r="C26" t="n">
-        <v>0.2070491015911102</v>
+        <v>0.07691856473684311</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2390451282262802</v>
+        <v>0.3211172819137573</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7257912158966064</v>
+        <v>0.2204250991344452</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.202107787132263</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.05518556758761406</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.9679028987884521</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.3606323301792145</v>
       </c>
     </row>
     <row r="27">
@@ -848,16 +1144,28 @@
         <v>23</v>
       </c>
       <c r="B27" t="n">
-        <v>0.2070491015911102</v>
+        <v>0.3211172819137573</v>
       </c>
       <c r="C27" t="n">
-        <v>0.6550772786140442</v>
+        <v>0.2204250991344452</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7257912158966064</v>
+        <v>1.076062321662903</v>
       </c>
       <c r="E27" t="n">
-        <v>0.7940831780433655</v>
+        <v>0.09633518010377884</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-0.9679028987884521</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.3606323301792145</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.0490618608891964</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-0.2903708815574646</v>
       </c>
     </row>
     <row r="28">
@@ -865,16 +1173,28 @@
         <v>24</v>
       </c>
       <c r="B28" t="n">
-        <v>0.6550772786140442</v>
+        <v>1.076062321662903</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9015446305274963</v>
+        <v>0.09633518010377884</v>
       </c>
       <c r="D28" t="n">
-        <v>0.7940831780433655</v>
+        <v>-0.5247388482093811</v>
       </c>
       <c r="E28" t="n">
-        <v>0.652425229549408</v>
+        <v>0.3228186964988708</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.0490618608891964</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-0.2903708815574646</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.7062592506408691</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.01471855770796537</v>
       </c>
     </row>
     <row r="29">
@@ -882,16 +1202,28 @@
         <v>25</v>
       </c>
       <c r="B29" t="n">
-        <v>0.9015446305274963</v>
+        <v>-0.5247388482093811</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3541600704193115</v>
+        <v>0.3228186964988708</v>
       </c>
       <c r="D29" t="n">
-        <v>0.652425229549408</v>
+        <v>0.9373274445533752</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9047985076904297</v>
+        <v>-0.157421663403511</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.7062592506408691</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.01471855770796537</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.3163956105709076</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.2118777632713318</v>
       </c>
     </row>
     <row r="30">
@@ -899,16 +1231,28 @@
         <v>26</v>
       </c>
       <c r="B30" t="n">
-        <v>0.3541600704193115</v>
+        <v>0.9373274445533752</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9126355648040771</v>
+        <v>-0.157421663403511</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9047985076904297</v>
+        <v>-0.3874375224113464</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3436912894248962</v>
+        <v>0.2811982333660126</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.3163956105709076</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.2118777632713318</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.071729063987732</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.09491868317127228</v>
       </c>
     </row>
     <row r="31">
@@ -916,16 +1260,28 @@
         <v>27</v>
       </c>
       <c r="B31" t="n">
-        <v>0.9126355648040771</v>
+        <v>-0.3874375224113464</v>
       </c>
       <c r="C31" t="n">
-        <v>0.3181302845478058</v>
+        <v>0.2811982333660126</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3436912894248962</v>
+        <v>1.071047306060791</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9000146389007568</v>
+        <v>-0.1162312626838684</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.071729063987732</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.09491868317127228</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-0.5131258964538574</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.3215187191963196</v>
       </c>
     </row>
     <row r="32">
@@ -933,16 +1289,28 @@
         <v>28</v>
       </c>
       <c r="B32" t="n">
-        <v>0.3181302845478058</v>
+        <v>1.071047306060791</v>
       </c>
       <c r="C32" t="n">
-        <v>0.8655244112014771</v>
+        <v>-0.1162312626838684</v>
       </c>
       <c r="D32" t="n">
-        <v>0.9000146389007568</v>
+        <v>-0.7222303748130798</v>
       </c>
       <c r="E32" t="n">
-        <v>0.3590531945228577</v>
+        <v>0.3213141858577728</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-0.5131258964538574</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.3215187191963196</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.9529012441635132</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-0.1539377719163895</v>
       </c>
     </row>
     <row r="33">
@@ -950,16 +1318,28 @@
         <v>29</v>
       </c>
       <c r="B33" t="n">
-        <v>0.8655244112014771</v>
+        <v>-0.7222303748130798</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4644036889076233</v>
+        <v>0.3213141858577728</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3590531945228577</v>
+        <v>0.5910508036613464</v>
       </c>
       <c r="E33" t="n">
-        <v>0.918234646320343</v>
+        <v>-0.216669112443924</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.9529012441635132</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-0.1539377719163895</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-0.4251668751239777</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.285870373249054</v>
       </c>
     </row>
     <row r="34">
@@ -967,16 +1347,28 @@
         <v>30</v>
       </c>
       <c r="B34" t="n">
-        <v>0.4644036889076233</v>
+        <v>0.5910508036613464</v>
       </c>
       <c r="C34" t="n">
-        <v>0.9924442768096924</v>
+        <v>-0.216669112443924</v>
       </c>
       <c r="D34" t="n">
-        <v>0.918234646320343</v>
+        <v>0.2942534387111664</v>
       </c>
       <c r="E34" t="n">
-        <v>0.2995682954788208</v>
+        <v>0.1773152351379395</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-0.4251668751239777</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.285870373249054</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.032796740531921</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-0.1275500655174255</v>
       </c>
     </row>
     <row r="35">
@@ -984,16 +1376,28 @@
         <v>31</v>
       </c>
       <c r="B35" t="n">
-        <v>0.9924442768096924</v>
+        <v>0.2942534387111664</v>
       </c>
       <c r="C35" t="n">
-        <v>0.02991952002048492</v>
+        <v>0.1773152351379395</v>
       </c>
       <c r="D35" t="n">
-        <v>0.2995682954788208</v>
+        <v>1.056096076965332</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8372102379798889</v>
+        <v>0.08827603608369827</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.032796740531921</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-0.1275500655174255</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-0.6208868622779846</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.3098390400409698</v>
       </c>
     </row>
     <row r="36">
@@ -1001,16 +1405,28 @@
         <v>32</v>
       </c>
       <c r="B36" t="n">
-        <v>0.02991952002048492</v>
+        <v>1.056096076965332</v>
       </c>
       <c r="C36" t="n">
-        <v>0.1158071309328079</v>
+        <v>0.08827603608369827</v>
       </c>
       <c r="D36" t="n">
-        <v>0.8372102379798889</v>
+        <v>-0.4731985330581665</v>
       </c>
       <c r="E36" t="n">
-        <v>0.5437941551208496</v>
+        <v>0.3168288171291351</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-0.6208868622779846</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.3098390400409698</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.7701383233070374</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-0.1862660646438599</v>
       </c>
     </row>
     <row r="37">
@@ -1018,16 +1434,28 @@
         <v>33</v>
       </c>
       <c r="B37" t="n">
-        <v>0.1158071309328079</v>
+        <v>-0.4731985330581665</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4085593819618225</v>
+        <v>0.3168288171291351</v>
       </c>
       <c r="D37" t="n">
-        <v>0.5437941551208496</v>
+        <v>1.003345251083374</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9898474812507629</v>
+        <v>-0.1419595628976822</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.7701383233070374</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-0.1862660646438599</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-0.01662431657314301</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.2310414910316467</v>
       </c>
     </row>
     <row r="38">
@@ -1035,16 +1463,28 @@
         <v>34</v>
       </c>
       <c r="B38" t="n">
-        <v>0.4085593819618225</v>
+        <v>1.003345251083374</v>
       </c>
       <c r="C38" t="n">
-        <v>0.9641380906105042</v>
+        <v>-0.1419595628976822</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9898474812507629</v>
+        <v>-0.5513418912887573</v>
       </c>
       <c r="E38" t="n">
-        <v>0.04009731113910675</v>
+        <v>0.3010035753250122</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-0.01662431657314301</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.2310414910316467</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1.23065459728241</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-0.004987295251339674</v>
       </c>
     </row>
     <row r="39">
@@ -1052,16 +1492,28 @@
         <v>35</v>
       </c>
       <c r="B39" t="n">
-        <v>0.9641380906105042</v>
+        <v>-0.5513418912887573</v>
       </c>
       <c r="C39" t="n">
-        <v>0.1379576474428177</v>
+        <v>0.3010035753250122</v>
       </c>
       <c r="D39" t="n">
-        <v>0.04009731113910675</v>
+        <v>0.8754345178604126</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1535731703042984</v>
+        <v>-0.1654025763273239</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.23065459728241</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-0.004987295251339674</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-1.125302314758301</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.3691963851451874</v>
       </c>
     </row>
     <row r="40">
@@ -1069,16 +1521,28 @@
         <v>36</v>
       </c>
       <c r="B40" t="n">
-        <v>0.1379576474428177</v>
+        <v>0.8754345178604126</v>
       </c>
       <c r="C40" t="n">
-        <v>0.4745120704174042</v>
+        <v>-0.1654025763273239</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1535731703042984</v>
+        <v>-0.2383424043655396</v>
       </c>
       <c r="E40" t="n">
-        <v>0.518653929233551</v>
+        <v>0.2626303434371948</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-1.125302314758301</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.3691963851451874</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-0.4036309421062469</v>
+      </c>
+      <c r="I40" t="n">
+        <v>-0.3375906944274902</v>
       </c>
     </row>
     <row r="41">
@@ -1086,16 +1550,28 @@
         <v>37</v>
       </c>
       <c r="B41" t="n">
-        <v>0.4745120704174042</v>
+        <v>-0.2383424043655396</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9949079751968384</v>
+        <v>0.2626303434371948</v>
       </c>
       <c r="D41" t="n">
-        <v>0.518653929233551</v>
+        <v>1.183100461959839</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9961116313934326</v>
+        <v>-0.07150272279977798</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-0.4036309421062469</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-0.3375906944274902</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.4343242347240448</v>
+      </c>
+      <c r="I41" t="n">
+        <v>-0.1210892796516418</v>
       </c>
     </row>
     <row r="42">
@@ -1103,16 +1579,28 @@
         <v>38</v>
       </c>
       <c r="B42" t="n">
-        <v>0.9949079751968384</v>
+        <v>1.183100461959839</v>
       </c>
       <c r="C42" t="n">
-        <v>0.02021379582583904</v>
+        <v>-0.07150272279977798</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9961116313934326</v>
+        <v>-1.0311199426651</v>
       </c>
       <c r="E42" t="n">
-        <v>0.01545438170433044</v>
+        <v>0.3549301326274872</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.4343242347240448</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-0.1210892796516418</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.6148181557655334</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.1302972733974457</v>
       </c>
     </row>
     <row r="43">
@@ -1120,16 +1608,28 @@
         <v>39</v>
       </c>
       <c r="B43" t="n">
-        <v>0.02021379582583904</v>
+        <v>-1.0311199426651</v>
       </c>
       <c r="C43" t="n">
-        <v>0.07902273535728455</v>
+        <v>0.3549301326274872</v>
       </c>
       <c r="D43" t="n">
-        <v>0.01545438170433044</v>
+        <v>-0.1335615515708923</v>
       </c>
       <c r="E43" t="n">
-        <v>0.06071002036333084</v>
+        <v>-0.3093359768390656</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.6148181557655334</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.1302972733974457</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.6010953187942505</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.1844454556703568</v>
       </c>
     </row>
     <row r="44">
@@ -1137,252 +1637,404 @@
         <v>40</v>
       </c>
       <c r="B44" t="n">
-        <v>0.07902273535728455</v>
+        <v>-0.1335615515708923</v>
       </c>
       <c r="C44" t="n">
-        <v>0.2903847992420197</v>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
+        <v>-0.3093359768390656</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.6656898260116577</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-0.04006846621632576</v>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
         <v>41</v>
       </c>
       <c r="B45" t="n">
-        <v>0.2903847992420197</v>
+        <v>0.6656898260116577</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8221852779388428</v>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
+        <v>-0.04006846621632576</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.3395313620567322</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.199706956744194</v>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>42</v>
       </c>
       <c r="B46" t="n">
-        <v>0.8221852779388428</v>
+        <v>0.3395313620567322</v>
       </c>
       <c r="C46" t="n">
-        <v>0.583324670791626</v>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+        <v>0.199706956744194</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1.038312792778015</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.1018594056367874</v>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
         <v>43</v>
       </c>
       <c r="B47" t="n">
-        <v>0.583324670791626</v>
+        <v>1.038312792778015</v>
       </c>
       <c r="C47" t="n">
-        <v>0.9697974324226379</v>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+        <v>0.1018594056367874</v>
+      </c>
+      <c r="D47" t="n">
+        <v>-0.4074714183807373</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.311493843793869</v>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
         <v>44</v>
       </c>
       <c r="B48" t="n">
-        <v>0.9697974324226379</v>
+        <v>-0.4074714183807373</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1168686375021935</v>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
+        <v>0.311493843793869</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1.079047679901123</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-0.122241422533989</v>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
         <v>45</v>
       </c>
       <c r="B49" t="n">
-        <v>0.1168686375021935</v>
+        <v>1.079047679901123</v>
       </c>
       <c r="C49" t="n">
-        <v>0.4118093252182007</v>
-      </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+        <v>-0.122241422533989</v>
+      </c>
+      <c r="D49" t="n">
+        <v>-0.7523229122161865</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.3237143158912659</v>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
         <v>46</v>
       </c>
       <c r="B50" t="n">
-        <v>0.4118093252182007</v>
+        <v>-0.7523229122161865</v>
       </c>
       <c r="C50" t="n">
-        <v>0.9664673805236816</v>
-      </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
+        <v>0.3237143158912659</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.5313286185264587</v>
+      </c>
+      <c r="E50" t="n">
+        <v>-0.2256968766450882</v>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
         <v>47</v>
       </c>
       <c r="B51" t="n">
-        <v>0.9664673805236816</v>
+        <v>0.5313286185264587</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1293085962533951</v>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
+        <v>-0.2256968766450882</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.3790690302848816</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.1593985706567764</v>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
         <v>48</v>
       </c>
       <c r="B52" t="n">
-        <v>0.1293085962533951</v>
+        <v>0.3790690302848816</v>
       </c>
       <c r="C52" t="n">
-        <v>0.4492256641387939</v>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
+        <v>0.1593985706567764</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.9582279324531555</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.1137207075953484</v>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
         <v>49</v>
       </c>
       <c r="B53" t="n">
-        <v>0.4492256641387939</v>
+        <v>0.9582279324531555</v>
       </c>
       <c r="C53" t="n">
-        <v>0.987213671207428</v>
-      </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+        <v>0.1137207075953484</v>
+      </c>
+      <c r="D53" t="n">
+        <v>-0.1717603653669357</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.2874683737754822</v>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
         <v>50</v>
       </c>
       <c r="B54" t="n">
-        <v>0.987213671207428</v>
+        <v>-0.1717603653669357</v>
       </c>
       <c r="C54" t="n">
-        <v>0.05036522820591927</v>
-      </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
+        <v>0.2874683737754822</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1.246166110038757</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-0.05152811110019684</v>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
         <v>51</v>
       </c>
       <c r="B55" t="n">
-        <v>0.05036522820591927</v>
+        <v>1.246166110038757</v>
       </c>
       <c r="C55" t="n">
-        <v>0.1908360123634338</v>
-      </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
+        <v>-0.05152811110019684</v>
+      </c>
+      <c r="D55" t="n">
+        <v>-1.225630044937134</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.3738498389720917</v>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
         <v>52</v>
       </c>
       <c r="B56" t="n">
-        <v>0.1908360123634338</v>
+        <v>-1.225630044937134</v>
       </c>
       <c r="C56" t="n">
-        <v>0.6161262989044189</v>
-      </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
+        <v>0.3738498389720917</v>
+      </c>
+      <c r="D56" t="n">
+        <v>-0.7291868329048157</v>
+      </c>
+      <c r="E56" t="n">
+        <v>-0.3676890134811401</v>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
         <v>53</v>
       </c>
       <c r="B57" t="n">
-        <v>0.6161262989044189</v>
+        <v>-0.7291868329048157</v>
       </c>
       <c r="C57" t="n">
-        <v>0.9436935782432556</v>
-      </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
+        <v>-0.3676890134811401</v>
+      </c>
+      <c r="D57" t="n">
+        <v>-0.1120878010988235</v>
+      </c>
+      <c r="E57" t="n">
+        <v>-0.2187560498714447</v>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
         <v>54</v>
       </c>
       <c r="B58" t="n">
-        <v>0.9436935782432556</v>
+        <v>-0.1120878010988235</v>
       </c>
       <c r="C58" t="n">
-        <v>0.2120127230882645</v>
-      </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
+        <v>-0.2187560498714447</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.7636548280715942</v>
+      </c>
+      <c r="E58" t="n">
+        <v>-0.03362634032964706</v>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
         <v>55</v>
       </c>
       <c r="B59" t="n">
-        <v>0.2120127230882645</v>
+        <v>0.7636548280715942</v>
       </c>
       <c r="C59" t="n">
-        <v>0.6665827035903931</v>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
+        <v>-0.03362634032964706</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.1499375253915787</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.2290964424610138</v>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
         <v>56</v>
       </c>
       <c r="B60" t="n">
-        <v>0.6665827035903931</v>
+        <v>0.1499375253915787</v>
       </c>
       <c r="C60" t="n">
-        <v>0.8867783546447754</v>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
+        <v>0.2290964424610138</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1.197622656822205</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.04498125985264778</v>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
         <v>57</v>
       </c>
       <c r="B61" t="n">
-        <v>0.8867783546447754</v>
+        <v>1.197622656822205</v>
       </c>
       <c r="C61" t="n">
-        <v>0.4006060659885406</v>
-      </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
+        <v>0.04498125985264778</v>
+      </c>
+      <c r="D61" t="n">
+        <v>-0.9630388617515564</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.3592868149280548</v>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
         <v>58</v>
       </c>
       <c r="B62" t="n">
-        <v>0.4006060659885406</v>
+        <v>-0.9630388617515564</v>
       </c>
       <c r="C62" t="n">
-        <v>0.9580821990966797</v>
-      </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
+        <v>0.3592868149280548</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0.06086546182632446</v>
+      </c>
+      <c r="E62" t="n">
+        <v>-0.2889116406440735</v>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="F1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/discrete_pinn/output_dir/dataset_splits.xlsx
+++ b/discrete_pinn/output_dir/dataset_splits.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data_Splits" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Data_Splits_henon_map" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
